--- a/site/leagues/proliga/2026_2027/xlsx/shot_packs/shot_pack_SBC.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/shot_packs/shot_pack_SBC.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -451,7 +451,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,42 +590,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="D2" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="E2" t="n">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -633,28 +633,28 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -663,10 +663,10 @@
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -757,12 +757,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBC_D._HALL</t>
+          <t>SBC_M._TERRY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D. Hall</t>
+          <t>M. Terry</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -771,29 +771,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -802,12 +802,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SBC_M._TERRY</t>
+          <t>SBC_D._HALL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M. Terry</t>
+          <t>D. Hall</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -816,29 +816,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -847,12 +847,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SBC_M._TERRY</t>
+          <t>SBC_D._HALL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Terry</t>
+          <t>D. Hall</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -861,17 +861,17 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" t="n">
-        <v>20</v>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -879,11 +879,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -892,39 +892,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SBC_M._TAVARES</t>
+          <t>SBC_M._TERRY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Tavares</t>
+          <t>M. Terry</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -937,50 +937,140 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBC_M._TERRY</t>
+          <t>SBC_M._TAVARES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Terry</t>
+          <t>M. Tavares</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SBC_M._TERRY</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M. Terry</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SBC_M._TAVARES</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M. Tavares</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K6"/>
+  <autoFilter ref="A1:K8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -995,7 +1085,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1018,7 +1108,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: M. Terry (43 L)</t>
+          <t>Maior volume: M. Terry (56 L)</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1120,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: M. Tavares (16 3PA)</t>
+          <t>Maior volume 3pt: M. Tavares (25 3PA)</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1132,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: T. Espada (1.6 pts/shot)</t>
+          <t>Mais eficaz: T. Espada (1.2 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1144,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Paint Non-RA (35 L)</t>
+          <t>Zona mais usada: Paint Non-RA (64 L)</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1156,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Paint Non-RA (68.6%)</t>
+          <t>Zona mais eficaz: Restricted Area (61.5%)</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1215,30 +1305,30 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E2" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1250,31 +1340,31 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>20</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>17</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>12</v>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -1292,17 +1382,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1315,7 +1405,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1323,11 +1413,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1336,11 +1426,11 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -1350,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -1365,66 +1455,66 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>28.0%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>69.4%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
         <v>16</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>43.8%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>76.2%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>9</v>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1442,34 +1532,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1477,24 +1567,24 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>6</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1519,7 +1609,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1533,7 +1623,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1542,7 +1632,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1550,24 +1640,24 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1578,7 +1668,7 @@
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1587,60 +1677,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SBC_D._TAVARES</t>
+          <t>SBC_H._SMITH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Tavares</t>
+          <t>H. Smith</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>5</v>
       </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>9</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1655,221 +1745,308 @@
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBC_J._SMITH</t>
+          <t>SBC_D._TAVARES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Smith</t>
+          <t>D. Tavares</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBC_M._MBOUP</t>
+          <t>SBC_N._BARBOSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M. Mboup</t>
+          <t>N. Barbosa</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBC_N._BARBOSA</t>
+          <t>SBC_M._MBOUP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>N. Barbosa</t>
+          <t>M. Mboup</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="Q10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SBC_J._SMITH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Smith</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
-        <v>9</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
         <v>6</v>
       </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S10"/>
+  <autoFilter ref="A1:S11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1896,7 +2073,7 @@
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
@@ -2013,33 +2190,33 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -2048,24 +2225,24 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>6</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -2090,21 +2267,21 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -2121,11 +2298,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2134,11 +2311,11 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -2152,155 +2329,155 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SBC_M._TAVARES</t>
+          <t>SBC_M._TERRY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Tavares</t>
+          <t>M. Terry</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SBC_M._TERRY</t>
+          <t>SBC_M._TAVARES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Terry</t>
+          <t>M. Tavares</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2315,7 +2492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2418,29 +2595,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H2" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2448,11 +2625,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -2474,26 +2651,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="H3" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="I3" t="n">
         <v>1.1</v>
@@ -2504,11 +2681,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -2530,29 +2707,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2560,11 +2737,11 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -2577,19 +2754,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SBC_J._SMITH</t>
+          <t>SBC_H._SMITH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Smith</t>
+          <t>H. Smith</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2598,14 +2775,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -2616,247 +2793,253 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBC_A._NONGO</t>
+          <t>SBC_N._BARBOSA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Nongo</t>
+          <t>N. Barbosa</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SBC_D._TAVARES</t>
+          <t>SBC_J._SMITH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Tavares</t>
+          <t>J. Smith</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
       <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
         <v>5</v>
       </c>
-      <c r="H7" t="n">
-        <v>9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>6</v>
-      </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBC_N._BARBOSA</t>
+          <t>SBC_A._NONGO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>N. Barbosa</t>
+          <t>A. Nongo</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBC_D._HALL</t>
+          <t>SBC_D._TAVARES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D. Hall</t>
+          <t>D. Tavares</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBC_M._MBOUP</t>
+          <t>SBC_D._HALL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M. Mboup</t>
+          <t>D. Hall</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2872,34 +3055,84 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="H10" t="n">
+        <v>44</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>27</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>63.0%</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SBC_M._MBOUP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M. Mboup</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>8</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>9</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N10"/>
+  <autoFilter ref="A1:N11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2910,7 +3143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3004,117 +3237,173 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBC_M._TAVARES</t>
+          <t>SBC_T._ESPADA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M. Tavares</t>
+          <t>T. Espada</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H2" t="n">
+        <v>23</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>7</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>43.8%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>76.2%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>9</v>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>SBC_M._TAVARES</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M. Tavares</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>28.0%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>69.4%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H3" t="n">
+        <v>33</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>16</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>SBC_M._TERRY</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>M. Terry</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>13</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>23.1%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>30.2%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>43</v>
-      </c>
-      <c r="H3" t="n">
-        <v>49</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="C4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>26.8%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>56</v>
+      </c>
+      <c r="H4" t="n">
+        <v>63</v>
+      </c>
+      <c r="I4" t="n">
         <v>1.1</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
+      <c r="K4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
         <v>2</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N4" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N3"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3193,130 +3482,130 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D2" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3329,36 +3618,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3368,7 +3657,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
@@ -3378,22 +3667,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3408,7 +3697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3419,7 +3708,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -3528,53 +3817,53 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>17</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>12</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="J2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -3598,11 +3887,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3611,11 +3900,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -3624,7 +3913,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3632,11 +3921,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -3644,7 +3933,7 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
@@ -3664,57 +3953,57 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Corner 3 Right</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>7</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>57.1%</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="L4" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5">
@@ -3734,57 +4023,57 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>6</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Corner 3 Left</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="L5" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6">
@@ -3800,24 +4089,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -3838,7 +4127,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -3846,7 +4135,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3860,43 +4149,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SBC_D._TAVARES</t>
+          <t>SBC_H._SMITH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Tavares</t>
+          <t>H. Smith</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -3908,193 +4197,283 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBC_J._SMITH</t>
+          <t>SBC_D._TAVARES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Smith</t>
+          <t>D. Tavares</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBC_M._MBOUP</t>
+          <t>SBC_N._BARBOSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M. Mboup</t>
+          <t>N. Barbosa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
       <c r="P9" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBC_N._BARBOSA</t>
+          <t>SBC_M._MBOUP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>N. Barbosa</t>
+          <t>M. Mboup</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SBC_J._SMITH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Smith</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4105,7 +4484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4181,91 +4560,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBC_M._TERRY</t>
+          <t>SBC_D._HALL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M. Terry</t>
+          <t>D. Hall</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2" t="n">
         <v>17</v>
       </c>
-      <c r="E2" t="n">
-        <v>10</v>
-      </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SBC_D._HALL</t>
+          <t>SBC_M._TERRY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D. Hall</t>
+          <t>M. Terry</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -4281,92 +4660,92 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SBC_M._TERRY</t>
+          <t>SBC_M._TAVARES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Terry</t>
+          <t>M. Tavares</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBC_M._TAVARES</t>
+          <t>SBC_M._TERRY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Tavares</t>
+          <t>M. Terry</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4375,7 +4754,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -4385,22 +4764,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -4420,25 +4799,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -4461,85 +4840,220 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>SBC_M._TAVARES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M. Tavares</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>19.4%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>SBC_T._ESPADA</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>T. Espada</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>36.8%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SBC_T._ESPADA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T. Espada</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" t="n">
-        <v>9</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SBC_H._SMITH</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H. Smith</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K9"/>
+  <autoFilter ref="A1:K12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>